--- a/data/nzd0375/nzd0375.xlsx
+++ b/data/nzd0375/nzd0375.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F451"/>
+  <dimension ref="A1:F455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11252,6 +11252,102 @@
         <v>402.77</v>
       </c>
       <c r="F451" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:06:37+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>401.38</v>
+      </c>
+      <c r="C452" t="n">
+        <v>353.7</v>
+      </c>
+      <c r="D452" t="n">
+        <v>378.3</v>
+      </c>
+      <c r="E452" t="n">
+        <v>401.72</v>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>392.66</v>
+      </c>
+      <c r="C453" t="n">
+        <v>351.61</v>
+      </c>
+      <c r="D453" t="n">
+        <v>377.84</v>
+      </c>
+      <c r="E453" t="n">
+        <v>399.82</v>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:06:43+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>391.19</v>
+      </c>
+      <c r="C454" t="n">
+        <v>352.73</v>
+      </c>
+      <c r="D454" t="n">
+        <v>376.88</v>
+      </c>
+      <c r="E454" t="n">
+        <v>398.24</v>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>388.84</v>
+      </c>
+      <c r="C455" t="n">
+        <v>353.47</v>
+      </c>
+      <c r="D455" t="n">
+        <v>375.77</v>
+      </c>
+      <c r="E455" t="n">
+        <v>396.98</v>
+      </c>
+      <c r="F455" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11268,7 +11364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B505"/>
+  <dimension ref="A1:B509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16321,6 +16417,46 @@
       </c>
       <c r="B505" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>-0.52</v>
       </c>
     </row>
   </sheetData>
@@ -16489,28 +16625,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>6.829057128691369</v>
+        <v>6.739008394406088</v>
       </c>
       <c r="J2" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="K2" t="n">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="L2" t="n">
-        <v>0.656907314914519</v>
+        <v>0.6519616868866129</v>
       </c>
       <c r="M2" t="n">
-        <v>31.54595824290756</v>
+        <v>31.58764600180872</v>
       </c>
       <c r="N2" t="n">
-        <v>1426.076417901698</v>
+        <v>1436.451242705336</v>
       </c>
       <c r="O2" t="n">
-        <v>37.76342698831368</v>
+        <v>37.90054409510945</v>
       </c>
       <c r="P2" t="n">
-        <v>261.5385233110309</v>
+        <v>262.448844277905</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16567,28 +16703,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.402672176869107</v>
+        <v>3.366786765082677</v>
       </c>
       <c r="J3" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="K3" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9008131055189983</v>
+        <v>0.8963851110275315</v>
       </c>
       <c r="M3" t="n">
-        <v>7.241715204223171</v>
+        <v>7.40705437633346</v>
       </c>
       <c r="N3" t="n">
-        <v>74.2381134108346</v>
+        <v>77.21231548016723</v>
       </c>
       <c r="O3" t="n">
-        <v>8.616154212340597</v>
+        <v>8.787053856678428</v>
       </c>
       <c r="P3" t="n">
-        <v>282.0474642689373</v>
+        <v>282.4116311427564</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16645,28 +16781,28 @@
         <v>0.1297</v>
       </c>
       <c r="I4" t="n">
-        <v>3.61513576250742</v>
+        <v>3.608888383392061</v>
       </c>
       <c r="J4" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="K4" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8955939766567759</v>
+        <v>0.8970728302213609</v>
       </c>
       <c r="M4" t="n">
-        <v>7.652102597914521</v>
+        <v>7.628858683166687</v>
       </c>
       <c r="N4" t="n">
-        <v>88.72187741571636</v>
+        <v>88.05966936520527</v>
       </c>
       <c r="O4" t="n">
-        <v>9.419229130651635</v>
+        <v>9.384011368556907</v>
       </c>
       <c r="P4" t="n">
-        <v>283.6636343352895</v>
+        <v>283.7270522194386</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16723,28 +16859,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>4.37983210737293</v>
+        <v>4.358810325109194</v>
       </c>
       <c r="J5" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="K5" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8086495566722953</v>
+        <v>0.8096165762941364</v>
       </c>
       <c r="M5" t="n">
-        <v>13.27882548204136</v>
+        <v>13.25839790736133</v>
       </c>
       <c r="N5" t="n">
-        <v>264.332860568102</v>
+        <v>263.2773544620214</v>
       </c>
       <c r="O5" t="n">
-        <v>16.25831665850134</v>
+        <v>16.22582369132678</v>
       </c>
       <c r="P5" t="n">
-        <v>293.5809099085087</v>
+        <v>293.7942742360882</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16782,7 +16918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F451"/>
+  <dimension ref="A1:F455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31205,6 +31341,134 @@
         </is>
       </c>
     </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:06:37+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>-41.86833374650476,174.1614253441443</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>-41.86871447033311,174.16048991249733</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>-41.869377478842715,174.16053811591277</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>-41.87003171802337,174.1607363651555</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>-41.86829680270818,174.1613326327689</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>-41.868707460575486,174.16046654234782</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>-41.86937673887875,174.1605326626256</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>-41.87003021031327,174.16071356136524</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:06:43+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>-41.86829057478999,174.1613170036827</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>-41.86871121700123,174.1604790660637</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>-41.86937519460528,174.1605212818527</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>-41.870028956529836,174.1606945982141</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>-41.868280618589736,174.1612920184152</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>-41.868713698924616,174.16048734066243</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>-41.86937340903765,174.16050812283473</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-41.87002795667497,174.16067947570164</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0375/nzd0375.xlsx
+++ b/data/nzd0375/nzd0375.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F455"/>
+  <dimension ref="A1:F458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11348,6 +11348,78 @@
         <v>396.98</v>
       </c>
       <c r="F455" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>388</v>
+      </c>
+      <c r="C456" t="n">
+        <v>354.19</v>
+      </c>
+      <c r="D456" t="n">
+        <v>375.29</v>
+      </c>
+      <c r="E456" t="n">
+        <v>396.92</v>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:07:02+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>392.51</v>
+      </c>
+      <c r="C457" t="n">
+        <v>355.96</v>
+      </c>
+      <c r="D457" t="n">
+        <v>375.96</v>
+      </c>
+      <c r="E457" t="n">
+        <v>397.13</v>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>394.67</v>
+      </c>
+      <c r="C458" t="n">
+        <v>357.6</v>
+      </c>
+      <c r="D458" t="n">
+        <v>377.86</v>
+      </c>
+      <c r="E458" t="n">
+        <v>398.53</v>
+      </c>
+      <c r="F458" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11364,7 +11436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B509"/>
+  <dimension ref="A1:B512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16457,6 +16529,36 @@
       </c>
       <c r="B509" t="n">
         <v>-0.52</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -16625,28 +16727,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>6.739008394406088</v>
+        <v>6.671385087143923</v>
       </c>
       <c r="J2" t="n">
+        <v>457</v>
+      </c>
+      <c r="K2" t="n">
         <v>454</v>
       </c>
-      <c r="K2" t="n">
-        <v>451</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.6519616868866129</v>
+        <v>0.6480487887244102</v>
       </c>
       <c r="M2" t="n">
-        <v>31.58764600180872</v>
+        <v>31.61829411113458</v>
       </c>
       <c r="N2" t="n">
-        <v>1436.451242705336</v>
+        <v>1444.702587038754</v>
       </c>
       <c r="O2" t="n">
-        <v>37.90054409510945</v>
+        <v>38.0092434420728</v>
       </c>
       <c r="P2" t="n">
-        <v>262.448844277905</v>
+        <v>263.1348081779337</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16703,28 +16805,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.366786765082677</v>
+        <v>3.344595867192115</v>
       </c>
       <c r="J3" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="K3" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8963851110275315</v>
+        <v>0.8942632816724779</v>
       </c>
       <c r="M3" t="n">
-        <v>7.40705437633346</v>
+        <v>7.499521931873004</v>
       </c>
       <c r="N3" t="n">
-        <v>77.21231548016723</v>
+        <v>78.62137736563162</v>
       </c>
       <c r="O3" t="n">
-        <v>8.787053856678428</v>
+        <v>8.866869648620735</v>
       </c>
       <c r="P3" t="n">
-        <v>282.4116311427564</v>
+        <v>282.6376068891327</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16781,28 +16883,28 @@
         <v>0.1297</v>
       </c>
       <c r="I4" t="n">
-        <v>3.608888383392061</v>
+        <v>3.602951907519234</v>
       </c>
       <c r="J4" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="K4" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8970728302213609</v>
+        <v>0.89802289028299</v>
       </c>
       <c r="M4" t="n">
-        <v>7.628858683166687</v>
+        <v>7.620505682720092</v>
       </c>
       <c r="N4" t="n">
-        <v>88.05966936520527</v>
+        <v>87.62441758640827</v>
       </c>
       <c r="O4" t="n">
-        <v>9.384011368556907</v>
+        <v>9.360791504269725</v>
       </c>
       <c r="P4" t="n">
-        <v>283.7270522194386</v>
+        <v>283.7874949972589</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16859,28 +16961,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>4.358810325109194</v>
+        <v>4.341121437130874</v>
       </c>
       <c r="J5" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="K5" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8096165762941364</v>
+        <v>0.8100012525942455</v>
       </c>
       <c r="M5" t="n">
-        <v>13.25839790736133</v>
+        <v>13.25248722216974</v>
       </c>
       <c r="N5" t="n">
-        <v>263.2773544620214</v>
+        <v>262.7615644867755</v>
       </c>
       <c r="O5" t="n">
-        <v>16.22582369132678</v>
+        <v>16.20992179150706</v>
       </c>
       <c r="P5" t="n">
-        <v>293.7942742360882</v>
+        <v>293.9744114466394</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16918,7 +17020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F455"/>
+  <dimension ref="A1:F458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31469,6 +31571,102 @@
         </is>
       </c>
     </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>-41.868277059776375,174.1612830875129</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>-41.86871611376841,174.160495391624</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>-41.869372636899826,174.1605024324488</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>-41.87002790906278,174.160678755582</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:07:02+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>-41.868296167206424,174.16133103796403</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>-41.86872205025697,174.16051518357372</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>-41.869373714675454,174.16051037527922</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>-41.87002807570541,174.16068127600073</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>-41.868305318429535,174.16135400315684</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>-41.868727550729155,174.16053352188064</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>-41.869376771051094,174.160532899725</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>-41.87002918665488,174.16069807879242</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0375/nzd0375.xlsx
+++ b/data/nzd0375/nzd0375.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F458"/>
+  <dimension ref="A1:F459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11417,9 +11417,33 @@
         <v>377.86</v>
       </c>
       <c r="E458" t="n">
-        <v>398.53</v>
+        <v>401.49</v>
       </c>
       <c r="F458" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>400.59</v>
+      </c>
+      <c r="C459" t="n">
+        <v>359.11</v>
+      </c>
+      <c r="D459" t="n">
+        <v>378.62</v>
+      </c>
+      <c r="E459" t="n">
+        <v>401.52</v>
+      </c>
+      <c r="F459" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11436,7 +11460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B512"/>
+  <dimension ref="A1:B513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16559,6 +16583,16 @@
       </c>
       <c r="B512" t="n">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>
@@ -16727,28 +16761,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>6.671385087143923</v>
+        <v>6.652928686511936</v>
       </c>
       <c r="J2" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K2" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6480487887244102</v>
+        <v>0.6473107150925508</v>
       </c>
       <c r="M2" t="n">
-        <v>31.61829411113458</v>
+        <v>31.61335483257593</v>
       </c>
       <c r="N2" t="n">
-        <v>1444.702587038754</v>
+        <v>1445.534747287219</v>
       </c>
       <c r="O2" t="n">
-        <v>38.0092434420728</v>
+        <v>38.02018868032113</v>
       </c>
       <c r="P2" t="n">
-        <v>263.1348081779337</v>
+        <v>263.3226818308019</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16805,28 +16839,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.344595867192115</v>
+        <v>3.338614997453021</v>
       </c>
       <c r="J3" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K3" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8942632816724779</v>
+        <v>0.8938971566986691</v>
       </c>
       <c r="M3" t="n">
-        <v>7.499521931873004</v>
+        <v>7.521031988924719</v>
       </c>
       <c r="N3" t="n">
-        <v>78.62137736563162</v>
+        <v>78.87017363021953</v>
       </c>
       <c r="O3" t="n">
-        <v>8.866869648620735</v>
+        <v>8.880888110443658</v>
       </c>
       <c r="P3" t="n">
-        <v>282.6376068891327</v>
+        <v>282.6987251216334</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16883,28 +16917,28 @@
         <v>0.1297</v>
       </c>
       <c r="I4" t="n">
-        <v>3.602951907519234</v>
+        <v>3.601856043601873</v>
       </c>
       <c r="J4" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K4" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L4" t="n">
-        <v>0.89802289028299</v>
+        <v>0.8984149931238272</v>
       </c>
       <c r="M4" t="n">
-        <v>7.620505682720092</v>
+        <v>7.611537740236311</v>
       </c>
       <c r="N4" t="n">
-        <v>87.62441758640827</v>
+        <v>87.44721377450193</v>
       </c>
       <c r="O4" t="n">
-        <v>9.360791504269725</v>
+        <v>9.351321498831163</v>
       </c>
       <c r="P4" t="n">
-        <v>283.7874949972589</v>
+        <v>283.7986935801762</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16961,28 +16995,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>4.341121437130874</v>
+        <v>4.338183749924196</v>
       </c>
       <c r="J5" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K5" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8100012525942455</v>
+        <v>0.8105327117046683</v>
       </c>
       <c r="M5" t="n">
-        <v>13.25248722216974</v>
+        <v>13.23686106462618</v>
       </c>
       <c r="N5" t="n">
-        <v>262.7615644867755</v>
+        <v>262.2528579791966</v>
       </c>
       <c r="O5" t="n">
-        <v>16.20992179150706</v>
+        <v>16.19422298164369</v>
       </c>
       <c r="P5" t="n">
-        <v>293.9744114466394</v>
+        <v>294.0044556403592</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17020,7 +17054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F458"/>
+  <dimension ref="A1:F459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31658,10 +31692,42 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>-41.87002918665488,174.16069807879242</t>
+          <t>-41.87003153551132,174.1607336046966</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>-41.868330399535516,174.16141694482954</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>-41.86873261518567,174.160550406544</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>-41.86937799360011,174.16054190950393</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-41.87003155931724,174.16073396475645</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
